--- a/cds_files/Cincinnati_CDS_2025-2026.xlsx
+++ b/cds_files/Cincinnati_CDS_2025-2026.xlsx
@@ -434,7 +434,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>34447</v>
+        <v>30963</v>
       </c>
     </row>
     <row r="5">
@@ -496,10 +496,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.79</v>
+        <v>0.765</v>
       </c>
       <c r="C3" t="n">
-        <v>0.79</v>
+        <v>0.765</v>
       </c>
     </row>
     <row r="4">
@@ -509,10 +509,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.21</v>
+        <v>0.235</v>
       </c>
       <c r="C4" t="n">
-        <v>0.21</v>
+        <v>0.235</v>
       </c>
     </row>
     <row r="5">
@@ -522,10 +522,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="C5" t="n">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
     </row>
   </sheetData>
